--- a/product_surveys/012_mobile_network_connectivity_survey--product_surveys.xlsx
+++ b/product_surveys/012_mobile_network_connectivity_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,12 +767,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'no_coverage'}</t>
+          <t>no_coverage</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'No Coverage'}</t>
+          <t>No Coverage</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'always_on'}</t>
+          <t>always_on</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Always On'}</t>
+          <t>Always On</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'most_of_the_time'}</t>
+          <t>most_of_the_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Most of the time'}</t>
+          <t>Most of the time</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'rural_area'}</t>
+          <t>rural_area</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Rural Area'}</t>
+          <t>Rural Area</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'urban_area'}</t>
+          <t>urban_area</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Urban Area'}</t>
+          <t>Urban Area</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'suburban_area'}</t>
+          <t>suburban_area</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Suburban Area'}</t>
+          <t>Suburban Area</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'mobile_phone'}</t>
+          <t>mobile_phone</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Mobile Phone'}</t>
+          <t>Mobile Phone</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'tablet'}</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Tablet'}</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Laptop'}</t>
+          <t>Laptop</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'desktop'}</t>
+          <t>desktop</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Desktop'}</t>
+          <t>Desktop</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
